--- a/artfynd/A 13033-2026 artfynd.xlsx
+++ b/artfynd/A 13033-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2168,6 +2168,787 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132554290</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91313</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4189</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Geastrum pectinatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lindsberg, Lindsberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>591632</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6668481</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Karla Alfaro Gripe, Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132567684</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91855</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lilla Bårsjön, Lilla Bolandsmosse, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>592261</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6668513</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz, Max Karlsson, Janka Réthi, Karla Alfaro Gripe, Erik Christiansson, Valdemar Eklund, Alec Bailey, Joel Nilsson, Valdemar Fredén Zander, Elias Yngvesson, Malte Lindberg, Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132566670</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57136</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Rudtjärnssjön, Rudtjärnssjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>592366</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6668538</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Karla Alfaro Gripe, Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132561918</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92505</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1179</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gräddticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Perenniporia subacida</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Peck) Donk</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Rudtjärnssjön, Rudtjärnssjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>592173</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6668518</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Karla Alfaro Gripe, Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132567957</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91892</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lindsberg, Lindsberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>591825</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6668468</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Karla Alfaro Gripe, Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132556382</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92191</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>658</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lindsberg, Lindsberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>591788</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6668474</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Karla Alfaro Gripe, Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132558343</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92264</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lindsberg, Lindsberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>591959</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6668553</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Karla Alfaro Gripe, Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132556404</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91892</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lindsberg, Lindsberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>591843</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6668478</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Karla Alfaro Gripe, Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13033-2026 artfynd.xlsx
+++ b/artfynd/A 13033-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2949,6 +2949,392 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132623113</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78328</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6000248</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mörk kådsvartspik</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis montana</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lindesberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>592243</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6668570</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>7 cm i diameter stubbe med stelnad kåda runt kanten</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies # 7 cm i diameter stubbe med stelnad kåda runt kanten</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elias Yngvesson, Joel Nilsson, Alec Bailey, Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132623089</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78328</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6000248</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mörk kådsvartspik</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis montana</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lindesbergs , Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>592345</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6668516</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Ca 15cm i diameter Stubbe med stelnad kåda längs kanten</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies # Ca 15cm i diameter Stubbe med stelnad kåda längs kanten</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Elias Yngvesson, Joel Nilsson, Alec Bailey, Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132623126</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78328</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6000248</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mörk kådsvartspik</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis montana</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lindesberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>592161</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6668543</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elias Yngvesson, Joel Nilsson, Alec Bailey, Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13033-2026 artfynd.xlsx
+++ b/artfynd/A 13033-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132572412</v>
+        <v>132572416</v>
       </c>
       <c r="B2" t="n">
-        <v>4775</v>
+        <v>57137</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,30 +686,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -719,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591584</v>
+        <v>591920</v>
       </c>
       <c r="R2" t="n">
-        <v>6668441</v>
+        <v>6668491</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,7 +777,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132572416</v>
+        <v>132572412</v>
       </c>
       <c r="B3" t="n">
-        <v>57136</v>
+        <v>4775</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,29 +806,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -835,13 +839,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591920</v>
+        <v>591584</v>
       </c>
       <c r="R3" t="n">
-        <v>6668491</v>
+        <v>6668441</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,12 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,6 +893,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -912,57 +912,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132572421</v>
+        <v>132583654</v>
       </c>
       <c r="B4" t="n">
-        <v>4775</v>
+        <v>92511</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>1179</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>N. om Rudtjärnssjön, Vstm</t>
+          <t>Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592180</v>
+        <v>592172</v>
       </c>
       <c r="R4" t="n">
-        <v>6668526</v>
+        <v>6668466</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,70 +1004,75 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Max Karlsson, Alec Bailey, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132583654</v>
+        <v>132572421</v>
       </c>
       <c r="B5" t="n">
-        <v>92505</v>
+        <v>4775</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1179</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rudtjärnssjön, Vstm</t>
+          <t>N. om Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592172</v>
+        <v>592180</v>
       </c>
       <c r="R5" t="n">
-        <v>6668466</v>
+        <v>6668526</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,18 +1120,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Max Karlsson, Alec Bailey, Malte Lindberg, Elias Yngvesson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1259,7 +1259,7 @@
         <v>132583652</v>
       </c>
       <c r="B7" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132572418</v>
+        <v>132572419</v>
       </c>
       <c r="B8" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592028</v>
+        <v>592023</v>
       </c>
       <c r="R8" t="n">
-        <v>6668469</v>
+        <v>6668462</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1486,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132572419</v>
+        <v>132572418</v>
       </c>
       <c r="B9" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592023</v>
+        <v>592028</v>
       </c>
       <c r="R9" t="n">
-        <v>6668462</v>
+        <v>6668469</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1726,7 +1726,7 @@
         <v>132572417</v>
       </c>
       <c r="B11" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2063,48 +2063,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132572413</v>
+        <v>132554290</v>
       </c>
       <c r="B14" t="n">
-        <v>79317</v>
+        <v>91319</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4189</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>N. om Rudtjärnssjön, Vstm</t>
+          <t>Lindsberg, Lindsberg, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591641</v>
+        <v>591632</v>
       </c>
       <c r="R14" t="n">
-        <v>6668441</v>
+        <v>6668481</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2131,19 +2131,9 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:42</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,22 +2148,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132554290</v>
+        <v>132567684</v>
       </c>
       <c r="B15" t="n">
-        <v>91313</v>
+        <v>91861</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,34 +2171,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4189</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lindsberg, Lindsberg, Vstm</t>
+          <t>Lilla Bårsjön, Lilla Bolandsmosse, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>591632</v>
+        <v>592261</v>
       </c>
       <c r="R15" t="n">
-        <v>6668481</v>
+        <v>6668513</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,22 +2245,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Karla Alfaro Gripe, Alec Bailey</t>
+          <t>Nora Toftgård Shahnavaz, Max Karlsson, Janka Réthi, Karla Alfaro Gripe, Erik Christiansson, Valdemar Eklund, Viktor Olofsson, Alec Bailey, Joel Nilsson, Valdemar Fredén Zander, Elias Yngvesson, Malte Lindberg, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132567684</v>
+        <v>132566670</v>
       </c>
       <c r="B16" t="n">
-        <v>91855</v>
+        <v>57137</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2278,34 +2268,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilla Bårsjön, Lilla Bolandsmosse, Vstm</t>
+          <t>Rudtjärnssjön, Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592261</v>
+        <v>592366</v>
       </c>
       <c r="R16" t="n">
-        <v>6668513</v>
+        <v>6668538</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2352,62 +2347,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Max Karlsson, Janka Réthi, Karla Alfaro Gripe, Erik Christiansson, Valdemar Eklund, Alec Bailey, Joel Nilsson, Valdemar Fredén Zander, Elias Yngvesson, Malte Lindberg, Emilia Blixt</t>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132566670</v>
+        <v>132561918</v>
       </c>
       <c r="B17" t="n">
-        <v>57136</v>
+        <v>92511</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>1179</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rudtjärnssjön, Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592366</v>
+        <v>592173</v>
       </c>
       <c r="R17" t="n">
-        <v>6668538</v>
+        <v>6668518</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2459,52 +2449,52 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Karla Alfaro Gripe, Alec Bailey</t>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132561918</v>
+        <v>132567957</v>
       </c>
       <c r="B18" t="n">
-        <v>92505</v>
+        <v>91898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rudtjärnssjön, Rudtjärnssjön, Vstm</t>
+          <t>Lindsberg, Lindsberg, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592173</v>
+        <v>591825</v>
       </c>
       <c r="R18" t="n">
-        <v>6668518</v>
+        <v>6668468</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2556,17 +2546,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Karla Alfaro Gripe, Alec Bailey</t>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132567957</v>
+        <v>132556382</v>
       </c>
       <c r="B19" t="n">
-        <v>91892</v>
+        <v>92197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2574,21 +2564,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2598,10 +2588,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>591825</v>
+        <v>591788</v>
       </c>
       <c r="R19" t="n">
-        <v>6668468</v>
+        <v>6668474</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2653,39 +2643,39 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Karla Alfaro Gripe, Alec Bailey</t>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132556382</v>
+        <v>132558343</v>
       </c>
       <c r="B20" t="n">
-        <v>92191</v>
+        <v>92270</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2695,10 +2685,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>591788</v>
+        <v>591959</v>
       </c>
       <c r="R20" t="n">
-        <v>6668474</v>
+        <v>6668553</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2750,39 +2740,39 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Karla Alfaro Gripe, Alec Bailey</t>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132558343</v>
+        <v>132556404</v>
       </c>
       <c r="B21" t="n">
-        <v>92264</v>
+        <v>91898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2792,10 +2782,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>591959</v>
+        <v>591843</v>
       </c>
       <c r="R21" t="n">
-        <v>6668553</v>
+        <v>6668478</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2847,55 +2837,66 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Karla Alfaro Gripe, Alec Bailey</t>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132556404</v>
+        <v>132623113</v>
       </c>
       <c r="B22" t="n">
-        <v>91892</v>
+        <v>78330</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6000248</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kådsvartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis montana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lindsberg, Lindsberg, Vstm</t>
+          <t>Lindesberg, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>591843</v>
+        <v>592243</v>
       </c>
       <c r="R22" t="n">
-        <v>6668478</v>
+        <v>6668570</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2933,28 +2934,49 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>7 cm i diameter stubbe med stelnad kåda runt kanten</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies # 7 cm i diameter stubbe med stelnad kåda runt kanten</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Elias Yngvesson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Karla Alfaro Gripe, Alec Bailey</t>
+          <t>Elias Yngvesson, Joel Nilsson, Alec Bailey, Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132623113</v>
+        <v>132623089</v>
       </c>
       <c r="B23" t="n">
-        <v>78328</v>
+        <v>78330</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2981,29 +3003,33 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lindesberg, Vstm</t>
+          <t>Lindesbergs , Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592243</v>
+        <v>592345</v>
       </c>
       <c r="R23" t="n">
-        <v>6668570</v>
+        <v>6668516</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3057,12 +3083,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>7 cm i diameter stubbe med stelnad kåda runt kanten</t>
+          <t>Ca 15cm i diameter Stubbe med stelnad kåda längs kanten</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # 7 cm i diameter stubbe med stelnad kåda runt kanten</t>
+          <t>Picea abies # Ca 15cm i diameter Stubbe med stelnad kåda längs kanten</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3080,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132623089</v>
+        <v>132623126</v>
       </c>
       <c r="B24" t="n">
-        <v>78328</v>
+        <v>78330</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3110,7 +3136,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3118,22 +3144,18 @@
           <t>dm²</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lindesbergs , Vstm</t>
+          <t>Lindesberg, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592345</v>
+        <v>592161</v>
       </c>
       <c r="R24" t="n">
-        <v>6668516</v>
+        <v>6668543</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3188,14 +3210,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>Ca 15cm i diameter Stubbe med stelnad kåda längs kanten</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Ca 15cm i diameter Stubbe med stelnad kåda längs kanten</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3213,56 +3230,56 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132623126</v>
+        <v>132571742</v>
       </c>
       <c r="B25" t="n">
-        <v>78328</v>
+        <v>92197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6000248</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lindesberg, Vstm</t>
+          <t>V om Lilla Bårsjön, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592161</v>
+        <v>592476</v>
       </c>
       <c r="R25" t="n">
-        <v>6668543</v>
+        <v>6668574</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3307,6 +3324,16 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
       <c r="AJ25" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3317,23 +3344,1565 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elias Yngvesson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elias Yngvesson, Joel Nilsson, Alec Bailey, Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Emilia Blixt</t>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132574026</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97971</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>V om Lilla Bårsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>591977</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6668522</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132574711</v>
+      </c>
+      <c r="B27" t="n">
+        <v>8265</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>106456</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Granvivel</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pissodes harcyniae</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Herbst, 1795)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>V om Lilla Bårsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>591756</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6668460</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132574498</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91898</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>V om Lilla Bårsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>591831</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6668470</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132575149</v>
+      </c>
+      <c r="B29" t="n">
+        <v>5004</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>105212</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Barrpraktbagge</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Chrysobothris chrysostigma</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>V om Lilla Bårsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>592175</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6668478</v>
+      </c>
+      <c r="S29" t="n">
+        <v>50</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>1 år gamla angrepp</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132619243</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78330</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6000248</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk kådsvartspik</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis montana</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>V om Lilla Bårsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>591769</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6668486</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Barrnaturskog med fuktstråk</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Kåda på en gammal, fortfarande levande granstubbe # Picea abies</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132574506</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>V om Lilla Bårsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>591831</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6668470</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132574870</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91319</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4189</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Geastrum pectinatum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>V om Lilla Bårsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>591649</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6668446</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Barrmatta # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132574099</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>V om Lilla Bårsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>591934</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6668479</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Före detta torrgran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132574392</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57140</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>V om Lilla Bårsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>591897</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6668485</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132572413</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79319</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>N. om Rudtjärnssjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>591641</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6668441</v>
+      </c>
+      <c r="S35" t="n">
+        <v>6</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Nilsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Nilsson, Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132574583</v>
+      </c>
+      <c r="B36" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>V om Lilla Bårsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>591782</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6668502</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132619068</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78330</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6000248</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mörk kådsvartspik</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis montana</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lindsberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>591762</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6668479</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>K-, sp ~ 4x7</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Barrnaturskog med fuktstråk</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Kåda på en gammal, fortfarande levande granstubbe # Picea abies</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13033-2026 artfynd.xlsx
+++ b/artfynd/A 13033-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132572416</v>
+        <v>132572412</v>
       </c>
       <c r="B2" t="n">
-        <v>57137</v>
+        <v>4775</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,29 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591920</v>
+        <v>591584</v>
       </c>
       <c r="R2" t="n">
-        <v>6668491</v>
+        <v>6668441</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +773,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132572412</v>
+        <v>132572416</v>
       </c>
       <c r="B3" t="n">
-        <v>4775</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,30 +803,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -839,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591584</v>
+        <v>591920</v>
       </c>
       <c r="R3" t="n">
-        <v>6668441</v>
+        <v>6668491</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +880,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,7 +894,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -912,51 +912,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132583654</v>
+        <v>132572421</v>
       </c>
       <c r="B4" t="n">
-        <v>92511</v>
+        <v>4775</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1179</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rudtjärnssjön, Vstm</t>
+          <t>N. om Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592172</v>
+        <v>592180</v>
       </c>
       <c r="R4" t="n">
-        <v>6668466</v>
+        <v>6668526</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,75 +1010,70 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Max Karlsson, Alec Bailey, Malte Lindberg</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132572421</v>
+        <v>132583654</v>
       </c>
       <c r="B5" t="n">
-        <v>4775</v>
+        <v>92521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>1179</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>N. om Rudtjärnssjön, Vstm</t>
+          <t>Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592180</v>
+        <v>592172</v>
       </c>
       <c r="R5" t="n">
-        <v>6668526</v>
+        <v>6668466</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,19 +1121,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Max Karlsson, Alec Bailey, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1259,7 +1259,7 @@
         <v>132583652</v>
       </c>
       <c r="B7" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132572419</v>
+        <v>132572418</v>
       </c>
       <c r="B8" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592023</v>
+        <v>592028</v>
       </c>
       <c r="R8" t="n">
-        <v>6668462</v>
+        <v>6668469</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1486,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132572418</v>
+        <v>132572419</v>
       </c>
       <c r="B9" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592028</v>
+        <v>592023</v>
       </c>
       <c r="R9" t="n">
-        <v>6668469</v>
+        <v>6668462</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1726,7 +1726,7 @@
         <v>132572417</v>
       </c>
       <c r="B11" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>132554290</v>
       </c>
       <c r="B14" t="n">
-        <v>91319</v>
+        <v>91329</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>132567684</v>
       </c>
       <c r="B15" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>132566670</v>
       </c>
       <c r="B16" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>132561918</v>
       </c>
       <c r="B17" t="n">
-        <v>92511</v>
+        <v>92521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>132567957</v>
       </c>
       <c r="B18" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>132556382</v>
       </c>
       <c r="B19" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>132558343</v>
       </c>
       <c r="B20" t="n">
-        <v>92270</v>
+        <v>92280</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>132556404</v>
       </c>
       <c r="B21" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>132623113</v>
       </c>
       <c r="B22" t="n">
-        <v>78330</v>
+        <v>78338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>132623089</v>
       </c>
       <c r="B23" t="n">
-        <v>78330</v>
+        <v>78338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>132623126</v>
       </c>
       <c r="B24" t="n">
-        <v>78330</v>
+        <v>78338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>132571742</v>
       </c>
       <c r="B25" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>132574026</v>
       </c>
       <c r="B26" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>132574498</v>
       </c>
       <c r="B28" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>132619243</v>
       </c>
       <c r="B30" t="n">
-        <v>78330</v>
+        <v>78338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+          <t>Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Erik Christiansson, Emilia Blixt, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4159,7 +4159,7 @@
         <v>132574870</v>
       </c>
       <c r="B32" t="n">
-        <v>91319</v>
+        <v>91329</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+          <t>Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Erik Christiansson, Emilia Blixt, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4418,7 +4418,7 @@
         <v>132574392</v>
       </c>
       <c r="B34" t="n">
-        <v>57140</v>
+        <v>57144</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>132572413</v>
       </c>
       <c r="B35" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>132619068</v>
       </c>
       <c r="B37" t="n">
-        <v>78330</v>
+        <v>78338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 13033-2026 artfynd.xlsx
+++ b/artfynd/A 13033-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132572412</v>
+        <v>132572416</v>
       </c>
       <c r="B2" t="n">
-        <v>4775</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,30 +686,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -719,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591584</v>
+        <v>591920</v>
       </c>
       <c r="R2" t="n">
-        <v>6668441</v>
+        <v>6668491</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,7 +777,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132572416</v>
+        <v>132572412</v>
       </c>
       <c r="B3" t="n">
-        <v>57141</v>
+        <v>4775</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,29 +806,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -835,13 +839,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591920</v>
+        <v>591584</v>
       </c>
       <c r="R3" t="n">
-        <v>6668491</v>
+        <v>6668441</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,12 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,6 +893,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -912,57 +912,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132572421</v>
+        <v>132583654</v>
       </c>
       <c r="B4" t="n">
-        <v>4775</v>
+        <v>92522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>1179</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>N. om Rudtjärnssjön, Vstm</t>
+          <t>Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592180</v>
+        <v>592172</v>
       </c>
       <c r="R4" t="n">
-        <v>6668526</v>
+        <v>6668466</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,70 +1004,75 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Max Karlsson, Alec Bailey, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132583654</v>
+        <v>132572421</v>
       </c>
       <c r="B5" t="n">
-        <v>92521</v>
+        <v>4775</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1179</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rudtjärnssjön, Vstm</t>
+          <t>N. om Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592172</v>
+        <v>592180</v>
       </c>
       <c r="R5" t="n">
-        <v>6668466</v>
+        <v>6668526</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,18 +1120,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Max Karlsson, Alec Bailey, Malte Lindberg</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1259,7 +1259,7 @@
         <v>132583652</v>
       </c>
       <c r="B7" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132572418</v>
+        <v>132572419</v>
       </c>
       <c r="B8" t="n">
         <v>57141</v>
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592028</v>
+        <v>592023</v>
       </c>
       <c r="R8" t="n">
-        <v>6668469</v>
+        <v>6668462</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1486,7 +1486,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132572419</v>
+        <v>132572418</v>
       </c>
       <c r="B9" t="n">
         <v>57141</v>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592023</v>
+        <v>592028</v>
       </c>
       <c r="R9" t="n">
-        <v>6668462</v>
+        <v>6668469</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1726,7 +1726,7 @@
         <v>132572417</v>
       </c>
       <c r="B11" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>132554290</v>
       </c>
       <c r="B14" t="n">
-        <v>91329</v>
+        <v>91330</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>132567684</v>
       </c>
       <c r="B15" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>132561918</v>
       </c>
       <c r="B17" t="n">
-        <v>92521</v>
+        <v>92522</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>132567957</v>
       </c>
       <c r="B18" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>132556382</v>
       </c>
       <c r="B19" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>132558343</v>
       </c>
       <c r="B20" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>132556404</v>
       </c>
       <c r="B21" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>132571742</v>
       </c>
       <c r="B25" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3369,38 +3369,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132574026</v>
+        <v>132574498</v>
       </c>
       <c r="B26" t="n">
-        <v>97981</v>
+        <v>91909</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3408,10 +3407,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591977</v>
+        <v>591831</v>
       </c>
       <c r="R26" t="n">
-        <v>6668522</v>
+        <v>6668470</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3464,6 +3463,26 @@
       <c r="AI26" t="inlineStr">
         <is>
           <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3614,37 +3633,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132574498</v>
+        <v>132574026</v>
       </c>
       <c r="B28" t="n">
-        <v>91908</v>
+        <v>97982</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3652,10 +3672,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>591831</v>
+        <v>591977</v>
       </c>
       <c r="R28" t="n">
-        <v>6668470</v>
+        <v>6668522</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3708,26 +3728,6 @@
       <c r="AI28" t="inlineStr">
         <is>
           <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Erik Christiansson, Emilia Blixt, Malte Lindberg</t>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4159,7 +4159,7 @@
         <v>132574870</v>
       </c>
       <c r="B32" t="n">
-        <v>91329</v>
+        <v>91330</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Erik Christiansson, Emilia Blixt, Malte Lindberg</t>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 13033-2026 artfynd.xlsx
+++ b/artfynd/A 13033-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132572416</v>
+        <v>132572412</v>
       </c>
       <c r="B2" t="n">
-        <v>57141</v>
+        <v>4775</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,29 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591920</v>
+        <v>591584</v>
       </c>
       <c r="R2" t="n">
-        <v>6668491</v>
+        <v>6668441</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +773,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132572412</v>
+        <v>132572416</v>
       </c>
       <c r="B3" t="n">
-        <v>4775</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,30 +803,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -839,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591584</v>
+        <v>591920</v>
       </c>
       <c r="R3" t="n">
-        <v>6668441</v>
+        <v>6668491</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +880,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,7 +894,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1366,7 +1366,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132572419</v>
+        <v>132572418</v>
       </c>
       <c r="B8" t="n">
         <v>57141</v>
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592023</v>
+        <v>592028</v>
       </c>
       <c r="R8" t="n">
-        <v>6668462</v>
+        <v>6668469</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1486,7 +1486,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132572418</v>
+        <v>132572419</v>
       </c>
       <c r="B9" t="n">
         <v>57141</v>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592028</v>
+        <v>592023</v>
       </c>
       <c r="R9" t="n">
-        <v>6668469</v>
+        <v>6668462</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
+          <t>Malte Lindberg, Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Max Karlsson, Erik Christiansson, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -3500,39 +3500,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132574711</v>
+        <v>132574026</v>
       </c>
       <c r="B27" t="n">
-        <v>8265</v>
+        <v>97983</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106456</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granvivel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pissodes harcyniae</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Herbst, 1795)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3540,10 +3539,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591756</v>
+        <v>591977</v>
       </c>
       <c r="R27" t="n">
-        <v>6668460</v>
+        <v>6668522</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3596,26 +3595,6 @@
       <c r="AI27" t="inlineStr">
         <is>
           <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3633,38 +3612,39 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132574026</v>
+        <v>132574711</v>
       </c>
       <c r="B28" t="n">
-        <v>97982</v>
+        <v>8265</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>106456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granvivel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pissodes harcyniae</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Herbst, 1795)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3672,10 +3652,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>591977</v>
+        <v>591756</v>
       </c>
       <c r="R28" t="n">
-        <v>6668522</v>
+        <v>6668460</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3728,6 +3708,26 @@
       <c r="AI28" t="inlineStr">
         <is>
           <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 13033-2026 artfynd.xlsx
+++ b/artfynd/A 13033-2026 artfynd.xlsx
@@ -1723,48 +1723,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132572417</v>
+        <v>132583611</v>
       </c>
       <c r="B11" t="n">
-        <v>91909</v>
+        <v>4997</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100517</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Åttafläckig praktbagge</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buprestis octoguttata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N. om Rudtjärnssjön, Vstm</t>
+          <t>Lindsberg, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591929</v>
+        <v>591878</v>
       </c>
       <c r="R11" t="n">
-        <v>6668505</v>
+        <v>6668532</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1793,7 +1802,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,7 +1812,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,69 +1827,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Max Karlsson, Alec Bailey, Malte Lindberg, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132583611</v>
+        <v>132572417</v>
       </c>
       <c r="B12" t="n">
-        <v>4997</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100517</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Åttafläckig praktbagge</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buprestis octoguttata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lindsberg, Vstm</t>
+          <t>N. om Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591878</v>
+        <v>591929</v>
       </c>
       <c r="R12" t="n">
-        <v>6668532</v>
+        <v>6668505</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,12 +1934,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Max Karlsson, Alec Bailey, Malte Lindberg, Elias Yngvesson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 13033-2026 artfynd.xlsx
+++ b/artfynd/A 13033-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132572412</v>
+        <v>132572416</v>
       </c>
       <c r="B2" t="n">
-        <v>4775</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,30 +686,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -719,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591584</v>
+        <v>591920</v>
       </c>
       <c r="R2" t="n">
-        <v>6668441</v>
+        <v>6668491</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,7 +777,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132572416</v>
+        <v>132572412</v>
       </c>
       <c r="B3" t="n">
-        <v>57141</v>
+        <v>4775</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,29 +806,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -835,13 +839,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591920</v>
+        <v>591584</v>
       </c>
       <c r="R3" t="n">
-        <v>6668491</v>
+        <v>6668441</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,12 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,6 +893,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1366,7 +1366,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132572418</v>
+        <v>132572419</v>
       </c>
       <c r="B8" t="n">
         <v>57141</v>
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592028</v>
+        <v>592023</v>
       </c>
       <c r="R8" t="n">
-        <v>6668469</v>
+        <v>6668462</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1486,7 +1486,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132572419</v>
+        <v>132572418</v>
       </c>
       <c r="B9" t="n">
         <v>57141</v>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592023</v>
+        <v>592028</v>
       </c>
       <c r="R9" t="n">
-        <v>6668462</v>
+        <v>6668469</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1723,57 +1723,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132583611</v>
+        <v>132572417</v>
       </c>
       <c r="B11" t="n">
-        <v>4997</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100517</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Åttafläckig praktbagge</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buprestis octoguttata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lindsberg, Vstm</t>
+          <t>N. om Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591878</v>
+        <v>591929</v>
       </c>
       <c r="R11" t="n">
-        <v>6668532</v>
+        <v>6668505</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1802,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1812,7 +1803,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,60 +1818,69 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Max Karlsson, Alec Bailey, Malte Lindberg, Elias Yngvesson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132572417</v>
+        <v>132583611</v>
       </c>
       <c r="B12" t="n">
-        <v>91909</v>
+        <v>4997</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100517</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Åttafläckig praktbagge</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buprestis octoguttata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N. om Rudtjärnssjön, Vstm</t>
+          <t>Lindsberg, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591929</v>
+        <v>591878</v>
       </c>
       <c r="R12" t="n">
-        <v>6668505</v>
+        <v>6668532</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,12 +1934,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Max Karlsson, Alec Bailey, Malte Lindberg, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Max Karlsson, Erik Christiansson, Emilia Blixt</t>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -3493,45 +3493,46 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+          <t>Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Erik Christiansson, Emilia Blixt, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132574026</v>
+        <v>132574711</v>
       </c>
       <c r="B27" t="n">
-        <v>97983</v>
+        <v>8265</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>106456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granvivel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pissodes harcyniae</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Herbst, 1795)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3539,10 +3540,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591977</v>
+        <v>591756</v>
       </c>
       <c r="R27" t="n">
-        <v>6668522</v>
+        <v>6668460</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3595,6 +3596,26 @@
       <c r="AI27" t="inlineStr">
         <is>
           <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3612,39 +3633,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132574711</v>
+        <v>132574026</v>
       </c>
       <c r="B28" t="n">
-        <v>8265</v>
+        <v>97983</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106456</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granvivel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pissodes harcyniae</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Herbst, 1795)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3652,10 +3672,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>591756</v>
+        <v>591977</v>
       </c>
       <c r="R28" t="n">
-        <v>6668460</v>
+        <v>6668522</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3710,26 +3730,6 @@
           <t>Barrnaturskog</t>
         </is>
       </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
-      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+          <t>Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Erik Christiansson, Emilia Blixt, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+          <t>Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Erik Christiansson, Emilia Blixt, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+          <t>Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Erik Christiansson, Emilia Blixt, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+          <t>Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Erik Christiansson, Emilia Blixt, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 13033-2026 artfynd.xlsx
+++ b/artfynd/A 13033-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132572416</v>
       </c>
       <c r="B2" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>132583654</v>
       </c>
       <c r="B4" t="n">
-        <v>92522</v>
+        <v>92523</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>132583652</v>
       </c>
       <c r="B7" t="n">
-        <v>92208</v>
+        <v>92209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>132572419</v>
       </c>
       <c r="B8" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>132572418</v>
       </c>
       <c r="B9" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1723,48 +1723,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132572417</v>
+        <v>132583611</v>
       </c>
       <c r="B11" t="n">
-        <v>91909</v>
+        <v>4997</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100517</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Åttafläckig praktbagge</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buprestis octoguttata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N. om Rudtjärnssjön, Vstm</t>
+          <t>Lindsberg, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591929</v>
+        <v>591878</v>
       </c>
       <c r="R11" t="n">
-        <v>6668505</v>
+        <v>6668532</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1793,7 +1802,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,7 +1812,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,69 +1827,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Max Karlsson, Alec Bailey, Malte Lindberg, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132583611</v>
+        <v>132572417</v>
       </c>
       <c r="B12" t="n">
-        <v>4997</v>
+        <v>91910</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100517</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Åttafläckig praktbagge</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buprestis octoguttata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lindsberg, Vstm</t>
+          <t>N. om Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591878</v>
+        <v>591929</v>
       </c>
       <c r="R12" t="n">
-        <v>6668532</v>
+        <v>6668505</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,12 +1934,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Max Karlsson, Alec Bailey, Malte Lindberg, Elias Yngvesson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2066,7 +2066,7 @@
         <v>132554290</v>
       </c>
       <c r="B14" t="n">
-        <v>91330</v>
+        <v>91331</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>132567684</v>
       </c>
       <c r="B15" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>132566670</v>
       </c>
       <c r="B16" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>132561918</v>
       </c>
       <c r="B17" t="n">
-        <v>92522</v>
+        <v>92523</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>132567957</v>
       </c>
       <c r="B18" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>132556382</v>
       </c>
       <c r="B19" t="n">
-        <v>92208</v>
+        <v>92209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>132558343</v>
       </c>
       <c r="B20" t="n">
-        <v>92281</v>
+        <v>92282</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>132556404</v>
       </c>
       <c r="B21" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>132623113</v>
       </c>
       <c r="B22" t="n">
-        <v>78338</v>
+        <v>78339</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>132623089</v>
       </c>
       <c r="B23" t="n">
-        <v>78338</v>
+        <v>78339</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>132623126</v>
       </c>
       <c r="B24" t="n">
-        <v>78338</v>
+        <v>78339</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>132571742</v>
       </c>
       <c r="B25" t="n">
-        <v>92208</v>
+        <v>92209</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>132574498</v>
       </c>
       <c r="B26" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Erik Christiansson, Emilia Blixt, Malte Lindberg</t>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3636,7 +3636,7 @@
         <v>132574026</v>
       </c>
       <c r="B28" t="n">
-        <v>97983</v>
+        <v>97984</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Erik Christiansson, Emilia Blixt, Malte Lindberg</t>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3886,7 +3886,7 @@
         <v>132619243</v>
       </c>
       <c r="B30" t="n">
-        <v>78338</v>
+        <v>78339</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Erik Christiansson, Emilia Blixt, Malte Lindberg</t>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4159,7 +4159,7 @@
         <v>132574870</v>
       </c>
       <c r="B32" t="n">
-        <v>91330</v>
+        <v>91331</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Erik Christiansson, Emilia Blixt, Malte Lindberg</t>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4418,7 +4418,7 @@
         <v>132574392</v>
       </c>
       <c r="B34" t="n">
-        <v>57144</v>
+        <v>57145</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Erik Christiansson, Emilia Blixt, Malte Lindberg</t>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4529,7 +4529,7 @@
         <v>132572413</v>
       </c>
       <c r="B35" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>132619068</v>
       </c>
       <c r="B37" t="n">
-        <v>78338</v>
+        <v>78339</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 13033-2026 artfynd.xlsx
+++ b/artfynd/A 13033-2026 artfynd.xlsx
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
+          <t>Malte Lindberg, Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Max Karlsson, Erik Christiansson, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
+          <t>Malte Lindberg, Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Max Karlsson, Erik Christiansson, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 13033-2026 artfynd.xlsx
+++ b/artfynd/A 13033-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132572416</v>
+        <v>132572412</v>
       </c>
       <c r="B2" t="n">
-        <v>57145</v>
+        <v>4775</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,29 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591920</v>
+        <v>591584</v>
       </c>
       <c r="R2" t="n">
-        <v>6668491</v>
+        <v>6668441</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +773,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132572412</v>
+        <v>132572416</v>
       </c>
       <c r="B3" t="n">
-        <v>4775</v>
+        <v>57145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,30 +803,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -839,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591584</v>
+        <v>591920</v>
       </c>
       <c r="R3" t="n">
-        <v>6668441</v>
+        <v>6668491</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +880,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,7 +894,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1366,7 +1366,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132572419</v>
+        <v>132572418</v>
       </c>
       <c r="B8" t="n">
         <v>57145</v>
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592023</v>
+        <v>592028</v>
       </c>
       <c r="R8" t="n">
-        <v>6668462</v>
+        <v>6668469</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1486,7 +1486,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132572418</v>
+        <v>132572419</v>
       </c>
       <c r="B9" t="n">
         <v>57145</v>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592028</v>
+        <v>592023</v>
       </c>
       <c r="R9" t="n">
-        <v>6668469</v>
+        <v>6668462</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1723,48 +1723,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132572417</v>
+        <v>132583611</v>
       </c>
       <c r="B11" t="n">
-        <v>91918</v>
+        <v>4997</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100517</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Åttafläckig praktbagge</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buprestis octoguttata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N. om Rudtjärnssjön, Vstm</t>
+          <t>Lindsberg, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591929</v>
+        <v>591878</v>
       </c>
       <c r="R11" t="n">
-        <v>6668505</v>
+        <v>6668532</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1793,7 +1802,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,7 +1812,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,69 +1827,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Max Karlsson, Alec Bailey, Malte Lindberg, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132583611</v>
+        <v>132572417</v>
       </c>
       <c r="B12" t="n">
-        <v>4997</v>
+        <v>91918</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100517</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Åttafläckig praktbagge</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buprestis octoguttata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lindsberg, Vstm</t>
+          <t>N. om Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591878</v>
+        <v>591929</v>
       </c>
       <c r="R12" t="n">
-        <v>6668532</v>
+        <v>6668505</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,12 +1934,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Max Karlsson, Alec Bailey, Malte Lindberg, Elias Yngvesson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Max Karlsson, Erik Christiansson, Emilia Blixt</t>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Max Karlsson, Erik Christiansson, Emilia Blixt</t>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
+          <t>Malte Lindberg, Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Max Karlsson, Erik Christiansson, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+          <t>Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Erik Christiansson, Emilia Blixt, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 13033-2026 artfynd.xlsx
+++ b/artfynd/A 13033-2026 artfynd.xlsx
@@ -3362,17 +3362,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Erik Christiansson, Emilia Blixt, Malte Lindberg</t>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132574498</v>
+        <v>132574711</v>
       </c>
       <c r="B26" t="n">
-        <v>91918</v>
+        <v>8265</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3380,26 +3380,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>106456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granvivel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pissodes harcyniae</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Herbst, 1795)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3407,10 +3409,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591831</v>
+        <v>591756</v>
       </c>
       <c r="R26" t="n">
-        <v>6668470</v>
+        <v>6668460</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3477,12 +3479,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3500,10 +3502,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132574711</v>
+        <v>132574498</v>
       </c>
       <c r="B27" t="n">
-        <v>8265</v>
+        <v>91918</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3511,28 +3513,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106456</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granvivel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pissodes harcyniae</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Herbst, 1795)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591756</v>
+        <v>591831</v>
       </c>
       <c r="R27" t="n">
-        <v>6668460</v>
+        <v>6668470</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+          <t>Alec Bailey, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Emilia Blixt, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+          <t>Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Erik Christiansson, Emilia Blixt, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 13033-2026 artfynd.xlsx
+++ b/artfynd/A 13033-2026 artfynd.xlsx
@@ -3369,10 +3369,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132574711</v>
+        <v>132574498</v>
       </c>
       <c r="B26" t="n">
-        <v>8265</v>
+        <v>91918</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3380,28 +3380,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106456</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granvivel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pissodes harcyniae</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Herbst, 1795)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3409,10 +3407,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591756</v>
+        <v>591831</v>
       </c>
       <c r="R26" t="n">
-        <v>6668460</v>
+        <v>6668470</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3479,12 +3477,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3502,37 +3500,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132574498</v>
+        <v>132574026</v>
       </c>
       <c r="B27" t="n">
-        <v>91918</v>
+        <v>97995</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3540,10 +3539,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591831</v>
+        <v>591977</v>
       </c>
       <c r="R27" t="n">
-        <v>6668470</v>
+        <v>6668522</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3598,26 +3597,6 @@
           <t>Barrnaturskog</t>
         </is>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -3626,45 +3605,46 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alec Bailey, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Emilia Blixt, Malte Lindberg</t>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132574026</v>
+        <v>132574711</v>
       </c>
       <c r="B28" t="n">
-        <v>97995</v>
+        <v>8265</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>106456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granvivel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pissodes harcyniae</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Herbst, 1795)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3672,10 +3652,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>591977</v>
+        <v>591756</v>
       </c>
       <c r="R28" t="n">
-        <v>6668522</v>
+        <v>6668460</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3730,6 +3710,26 @@
           <t>Barrnaturskog</t>
         </is>
       </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Erik Christiansson, Emilia Blixt, Malte Lindberg</t>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander</t>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 13033-2026 artfynd.xlsx
+++ b/artfynd/A 13033-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>132572416</v>
       </c>
       <c r="B3" t="n">
-        <v>57145</v>
+        <v>57162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>132572418</v>
       </c>
       <c r="B8" t="n">
-        <v>57145</v>
+        <v>57162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>132572419</v>
       </c>
       <c r="B9" t="n">
-        <v>57145</v>
+        <v>57162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>132566670</v>
       </c>
       <c r="B16" t="n">
-        <v>57145</v>
+        <v>57162</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 13033-2026 artfynd.xlsx
+++ b/artfynd/A 13033-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132572412</v>
+        <v>132572425</v>
       </c>
       <c r="B2" t="n">
-        <v>4775</v>
+        <v>83350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100299</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>N. om Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591584</v>
+        <v>592573</v>
       </c>
       <c r="R2" t="n">
-        <v>6668441</v>
+        <v>6668615</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,7 +764,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,60 +775,52 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Joel Nilsson, Alec Bailey</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132572416</v>
+        <v>132556382</v>
       </c>
       <c r="B3" t="n">
-        <v>57162</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>N. om Rudtjärnssjön, Vstm</t>
+          <t>Lindsberg, Lindsberg, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591920</v>
+        <v>591788</v>
       </c>
       <c r="R3" t="n">
-        <v>6668491</v>
+        <v>6668474</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,24 +850,9 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,63 +867,71 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132583654</v>
+        <v>132571742</v>
       </c>
       <c r="B4" t="n">
-        <v>92531</v>
+        <v>92245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1179</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rudtjärnssjön, Vstm</t>
+          <t>V om Lilla Bårsjön, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592172</v>
+        <v>592476</v>
       </c>
       <c r="R4" t="n">
-        <v>6668466</v>
+        <v>6668574</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,96 +958,111 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Max Karlsson, Alec Bailey, Malte Lindberg</t>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132572421</v>
+        <v>132583652</v>
       </c>
       <c r="B5" t="n">
-        <v>4775</v>
+        <v>92245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>N. om Rudtjärnssjön, Vstm</t>
+          <t>Lindsberg, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592180</v>
+        <v>591798</v>
       </c>
       <c r="R5" t="n">
-        <v>6668526</v>
+        <v>6668507</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,76 +1110,66 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Max Karlsson, Alec Bailey, Malte Lindberg, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132572420</v>
+        <v>132572426</v>
       </c>
       <c r="B6" t="n">
-        <v>5179</v>
+        <v>81355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>1049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>N. om Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592148</v>
+        <v>592564</v>
       </c>
       <c r="R6" t="n">
-        <v>6668566</v>
+        <v>6668619</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,7 +1217,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1249,58 +1228,55 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Joel Nilsson, Alec Bailey</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132583652</v>
+        <v>132561918</v>
       </c>
       <c r="B7" t="n">
-        <v>92217</v>
+        <v>92559</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1179</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lindsberg, Vstm</t>
+          <t>Rudtjärnssjön, Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591798</v>
+        <v>592173</v>
       </c>
       <c r="R7" t="n">
-        <v>6668507</v>
+        <v>6668518</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,19 +1303,9 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,68 +1320,63 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Max Karlsson, Alec Bailey, Malte Lindberg, Elias Yngvesson</t>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132572418</v>
+        <v>132583654</v>
       </c>
       <c r="B8" t="n">
-        <v>57162</v>
+        <v>92559</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>1179</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N. om Rudtjärnssjön, Vstm</t>
+          <t>Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592028</v>
+        <v>592172</v>
       </c>
       <c r="R8" t="n">
-        <v>6668469</v>
+        <v>6668466</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,7 +1405,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,12 +1415,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,68 +1430,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Max Karlsson, Alec Bailey, Malte Lindberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132572419</v>
+        <v>132556404</v>
       </c>
       <c r="B9" t="n">
-        <v>57162</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>N. om Rudtjärnssjön, Vstm</t>
+          <t>Lindsberg, Lindsberg, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592023</v>
+        <v>591843</v>
       </c>
       <c r="R9" t="n">
-        <v>6668462</v>
+        <v>6668478</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,24 +1510,9 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,69 +1527,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132572428</v>
+        <v>132567957</v>
       </c>
       <c r="B10" t="n">
-        <v>4997</v>
+        <v>91974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100517</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Åttafläckig praktbagge</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Buprestis octoguttata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>N. om Rudtjärnssjön, Vstm</t>
+          <t>Lindsberg, Lindsberg, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591916</v>
+        <v>591825</v>
       </c>
       <c r="R10" t="n">
-        <v>6668456</v>
+        <v>6668468</v>
       </c>
       <c r="S10" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1683,97 +1607,77 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132583611</v>
+        <v>132572417</v>
       </c>
       <c r="B11" t="n">
-        <v>4997</v>
+        <v>91974</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100517</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Åttafläckig praktbagge</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buprestis octoguttata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lindsberg, Vstm</t>
+          <t>N. om Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591878</v>
+        <v>591929</v>
       </c>
       <c r="R11" t="n">
-        <v>6668532</v>
+        <v>6668505</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1802,7 +1706,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1812,7 +1716,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,22 +1731,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Max Karlsson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Max Karlsson, Alec Bailey, Malte Lindberg, Elias Yngvesson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132572417</v>
+        <v>132574498</v>
       </c>
       <c r="B12" t="n">
-        <v>91918</v>
+        <v>91974</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1868,19 +1772,22 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N. om Rudtjärnssjön, Vstm</t>
+          <t>V om Lilla Bårsjön, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591929</v>
+        <v>591831</v>
       </c>
       <c r="R12" t="n">
-        <v>6668505</v>
+        <v>6668470</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1907,96 +1814,108 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132572415</v>
+        <v>132558343</v>
       </c>
       <c r="B13" t="n">
-        <v>5179</v>
+        <v>92318</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>2062</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>N. om Rudtjärnssjön, Vstm</t>
+          <t>Lindsberg, Lindsberg, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591808</v>
+        <v>591959</v>
       </c>
       <c r="R13" t="n">
-        <v>6668490</v>
+        <v>6668553</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2023,50 +1942,39 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132554290</v>
+        <v>132572340</v>
       </c>
       <c r="B14" t="n">
-        <v>91339</v>
+        <v>96106</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,34 +1982,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4189</v>
+        <v>2558</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Krushättemossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Pers., nom.sanct</t>
-        </is>
-      </c>
+          <t>Ulota crispa s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lindsberg, Lindsberg, Vstm</t>
+          <t>V om Lilla Bårsjön, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591632</v>
+        <v>592437</v>
       </c>
       <c r="R14" t="n">
-        <v>6668481</v>
+        <v>6668605</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2142,28 +2054,59 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132567684</v>
+        <v>132554290</v>
       </c>
       <c r="B15" t="n">
-        <v>91881</v>
+        <v>91395</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,34 +2114,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>4189</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lilla Bårsjön, Lilla Bolandsmosse, Vstm</t>
+          <t>Lindsberg, Lindsberg, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592261</v>
+        <v>591632</v>
       </c>
       <c r="R15" t="n">
-        <v>6668513</v>
+        <v>6668481</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,22 +2188,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Max Karlsson, Janka Réthi, Karla Alfaro Gripe, Erik Christiansson, Valdemar Eklund, Viktor Olofsson, Alec Bailey, Joel Nilsson, Valdemar Fredén Zander, Elias Yngvesson, Malte Lindberg, Emilia Blixt</t>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132566670</v>
+        <v>132574870</v>
       </c>
       <c r="B16" t="n">
-        <v>57162</v>
+        <v>91395</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2268,39 +2211,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>4189</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rudtjärnssjön, Rudtjärnssjön, Vstm</t>
+          <t>V om Lilla Bårsjön, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592366</v>
+        <v>591649</v>
       </c>
       <c r="R16" t="n">
-        <v>6668538</v>
+        <v>6668446</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2341,66 +2282,95 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Barrmatta # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132561918</v>
+        <v>132583655</v>
       </c>
       <c r="B17" t="n">
-        <v>92531</v>
+        <v>93271</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1179</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rudtjärnssjön, Rudtjärnssjön, Vstm</t>
+          <t>Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592173</v>
+        <v>592058</v>
       </c>
       <c r="R17" t="n">
-        <v>6668518</v>
+        <v>6668596</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2427,9 +2397,19 @@
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2444,57 +2424,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
+          <t>Max Karlsson, Alec Bailey, Malte Lindberg, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132567957</v>
+        <v>132567684</v>
       </c>
       <c r="B18" t="n">
-        <v>91918</v>
+        <v>91937</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lindsberg, Lindsberg, Vstm</t>
+          <t>Lilla Bårsjön, Lilla Bolandsmosse, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591825</v>
+        <v>592261</v>
       </c>
       <c r="R18" t="n">
-        <v>6668468</v>
+        <v>6668513</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2541,60 +2521,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
+          <t>Nora Toftgård Shahnavaz, Max Karlsson, Janka Réthi, Karla Alfaro Gripe, Erik Christiansson, Valdemar Eklund, Viktor Olofsson, Alec Bailey, Joel Nilsson, Valdemar Fredén Zander, Elias Yngvesson, Malte Lindberg, Emilia Blixt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132556382</v>
+        <v>132572413</v>
       </c>
       <c r="B19" t="n">
-        <v>92217</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lindsberg, Lindsberg, Vstm</t>
+          <t>N. om Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>591788</v>
+        <v>591641</v>
       </c>
       <c r="R19" t="n">
-        <v>6668474</v>
+        <v>6668441</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2621,9 +2601,19 @@
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2638,57 +2628,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
+          <t>Joel Nilsson, Alec Bailey</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132558343</v>
+        <v>132572405</v>
       </c>
       <c r="B20" t="n">
-        <v>92290</v>
+        <v>75354</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2062</v>
+        <v>6427</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Glansfläck</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Diarthonis spadicea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Leight.) Frisch &amp; al.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lindsberg, Lindsberg, Vstm</t>
+          <t>V om Lilla Bårsjön, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>591959</v>
+        <v>592261</v>
       </c>
       <c r="R20" t="n">
-        <v>6668553</v>
+        <v>6668523</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2729,63 +2722,99 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Barrnaturskog med fukstråk</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132556404</v>
+        <v>132566670</v>
       </c>
       <c r="B21" t="n">
-        <v>91918</v>
+        <v>57162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lindsberg, Lindsberg, Vstm</t>
+          <t>Rudtjärnssjön, Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>591843</v>
+        <v>592366</v>
       </c>
       <c r="R21" t="n">
-        <v>6668478</v>
+        <v>6668538</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2837,66 +2866,63 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Alec Bailey, Karla Alfaro Gripe, Viktor Olofsson, Janka Réthi, Elias Yngvesson, Valdemar Fredén Zander, Valdemar Eklund, Joel Nilsson, Nora Toftgård Shahnavaz, Max Karlsson, Erik Christiansson, Emilia Blixt</t>
+          <t>Malte Lindberg, Emilia Blixt, Erik Christiansson, Max Karlsson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe, Alec Bailey</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132623113</v>
+        <v>132572416</v>
       </c>
       <c r="B22" t="n">
-        <v>78344</v>
+        <v>57162</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6000248</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lindesberg, Vstm</t>
+          <t>N. om Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592243</v>
+        <v>591920</v>
       </c>
       <c r="R22" t="n">
-        <v>6668570</v>
+        <v>6668491</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2923,113 +2949,100 @@
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>7 cm i diameter stubbe med stelnad kåda runt kanten</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies # 7 cm i diameter stubbe med stelnad kåda runt kanten</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elias Yngvesson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elias Yngvesson, Joel Nilsson, Alec Bailey, Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Emilia Blixt</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132623089</v>
+        <v>132572418</v>
       </c>
       <c r="B23" t="n">
-        <v>78344</v>
+        <v>57162</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6000248</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lindesbergs , Vstm</t>
+          <t>N. om Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592345</v>
+        <v>592028</v>
       </c>
       <c r="R23" t="n">
-        <v>6668516</v>
+        <v>6668469</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3056,109 +3069,100 @@
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Ca 15cm i diameter Stubbe med stelnad kåda längs kanten</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies # Ca 15cm i diameter Stubbe med stelnad kåda längs kanten</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elias Yngvesson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elias Yngvesson, Joel Nilsson, Alec Bailey, Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Emilia Blixt</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132623126</v>
+        <v>132572419</v>
       </c>
       <c r="B24" t="n">
-        <v>78344</v>
+        <v>57162</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6000248</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lindesberg, Vstm</t>
+          <t>N. om Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592161</v>
+        <v>592023</v>
       </c>
       <c r="R24" t="n">
-        <v>6668543</v>
+        <v>6668462</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3185,104 +3189,101 @@
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elias Yngvesson</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elias Yngvesson, Joel Nilsson, Alec Bailey, Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Emilia Blixt</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132571742</v>
+        <v>132572412</v>
       </c>
       <c r="B25" t="n">
-        <v>92217</v>
+        <v>4776</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>100299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>V om Lilla Bårsjön, Vstm</t>
+          <t>N. om Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592476</v>
+        <v>591584</v>
       </c>
       <c r="R25" t="n">
-        <v>6668574</v>
+        <v>6668441</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3309,9 +3310,19 @@
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3324,96 +3335,72 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
-      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132574498</v>
+        <v>132572421</v>
       </c>
       <c r="B26" t="n">
-        <v>91918</v>
+        <v>4776</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>V om Lilla Bårsjön, Vstm</t>
+          <t>N. om Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591831</v>
+        <v>592180</v>
       </c>
       <c r="R26" t="n">
-        <v>6668470</v>
+        <v>6668526</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3440,9 +3427,19 @@
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3455,55 +3452,25 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
-      </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132574026</v>
+        <v>132572427</v>
       </c>
       <c r="B27" t="n">
-        <v>97995</v>
+        <v>4776</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3511,41 +3478,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>100299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>V om Lilla Bårsjön, Vstm</t>
+          <t>N. om Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591977</v>
+        <v>592559</v>
       </c>
       <c r="R27" t="n">
-        <v>6668522</v>
+        <v>6668631</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3572,9 +3544,19 @@
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,78 +3569,72 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132574711</v>
+        <v>132572428</v>
       </c>
       <c r="B28" t="n">
-        <v>8265</v>
+        <v>4998</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106456</v>
+        <v>100517</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granvivel</t>
+          <t>Åttafläckig praktbagge</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pissodes harcyniae</t>
+          <t>Buprestis octoguttata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Herbst, 1795)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>V om Lilla Bårsjön, Vstm</t>
+          <t>N. om Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>591756</v>
+        <v>591916</v>
       </c>
       <c r="R28" t="n">
-        <v>6668460</v>
+        <v>6668456</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3685,9 +3661,19 @@
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3700,80 +3686,54 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
-      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132575149</v>
+        <v>132583611</v>
       </c>
       <c r="B29" t="n">
-        <v>5004</v>
+        <v>4998</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>105212</v>
+        <v>100517</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Åttafläckig praktbagge</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Buprestis octoguttata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -3781,17 +3741,17 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>V om Lilla Bårsjön, Vstm</t>
+          <t>Lindsberg, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592175</v>
+        <v>591878</v>
       </c>
       <c r="R29" t="n">
-        <v>6668478</v>
+        <v>6668532</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3818,14 +3778,19 @@
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>1 år gamla angrepp</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3834,100 +3799,75 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Max Karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+          <t>Max Karlsson, Alec Bailey, Malte Lindberg, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132619243</v>
+        <v>132572415</v>
       </c>
       <c r="B30" t="n">
-        <v>78344</v>
+        <v>5181</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6000248</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>V om Lilla Bårsjön, Vstm</t>
+          <t>N. om Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>591769</v>
+        <v>591808</v>
       </c>
       <c r="R30" t="n">
-        <v>6668486</v>
+        <v>6668490</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3954,14 +3894,19 @@
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3970,63 +3915,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Barrnaturskog med fuktstråk</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Kåda på en gammal, fortfarande levande granstubbe # Picea abies</t>
-        </is>
-      </c>
-      <c r="AQ30" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132574506</v>
+        <v>132572420</v>
       </c>
       <c r="B31" t="n">
-        <v>5199</v>
+        <v>5181</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4034,39 +3945,43 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>V om Lilla Bårsjön, Vstm</t>
+          <t>N. om Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591831</v>
+        <v>592148</v>
       </c>
       <c r="R31" t="n">
-        <v>6668470</v>
+        <v>6668566</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4096,9 +4011,19 @@
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4111,55 +4036,25 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
-      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132574870</v>
+        <v>132574099</v>
       </c>
       <c r="B32" t="n">
-        <v>91339</v>
+        <v>5181</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4167,26 +4062,28 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4189</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4194,10 +4091,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591649</v>
+        <v>591934</v>
       </c>
       <c r="R32" t="n">
-        <v>6668446</v>
+        <v>6668479</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4262,9 +4159,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Barrmatta # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Före detta torrgran # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4282,10 +4184,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132574099</v>
+        <v>132574583</v>
       </c>
       <c r="B33" t="n">
-        <v>5179</v>
+        <v>5181</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4322,10 +4224,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>591934</v>
+        <v>591782</v>
       </c>
       <c r="R33" t="n">
-        <v>6668479</v>
+        <v>6668502</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4392,12 +4294,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Före detta torrgran # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4415,10 +4317,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132574392</v>
+        <v>132572424</v>
       </c>
       <c r="B34" t="n">
-        <v>57148</v>
+        <v>44182</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4426,41 +4328,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102613</v>
+        <v>101735</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>V om Lilla Bårsjön, Vstm</t>
+          <t>N. om Rudtjärnssjön, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>591897</v>
+        <v>592571</v>
       </c>
       <c r="R34" t="n">
-        <v>6668485</v>
+        <v>6668581</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4487,87 +4394,92 @@
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+          <t>Joel Nilsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132572413</v>
+        <v>132574392</v>
       </c>
       <c r="B35" t="n">
-        <v>79333</v>
+        <v>57165</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>N. om Rudtjärnssjön, Vstm</t>
+          <t>V om Lilla Bårsjön, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>591641</v>
+        <v>591897</v>
       </c>
       <c r="R35" t="n">
-        <v>6668441</v>
+        <v>6668485</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4594,21 +4506,11 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:42</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:42</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4617,26 +4519,36 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Joel Nilsson</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Joel Nilsson, Alec Bailey</t>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132574583</v>
+        <v>132574990</v>
       </c>
       <c r="B36" t="n">
-        <v>5179</v>
+        <v>9422</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4644,21 +4556,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>105076</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sinodendron cylindricum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4669,14 +4581,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>V om Lilla Bårsjön, Vstm</t>
+          <t>Lindsberg, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>591782</v>
+        <v>591588</v>
       </c>
       <c r="R36" t="n">
-        <v>6668502</v>
+        <v>6668491</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4733,22 +4645,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vårtbjörk</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4766,51 +4673,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132619068</v>
+        <v>132575149</v>
       </c>
       <c r="B37" t="n">
-        <v>78344</v>
+        <v>5005</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6000248</v>
+        <v>105212</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lindsberg, Vstm</t>
+          <t>V om Lilla Bårsjön, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>591762</v>
+        <v>592175</v>
       </c>
       <c r="R37" t="n">
-        <v>6668479</v>
+        <v>6668478</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4844,7 +4753,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>K-, sp ~ 4x7</t>
+          <t>1 år gamla angrepp</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4853,11 +4762,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4868,7 +4773,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Barrnaturskog med fuktstråk</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -4881,14 +4786,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Kåda på en gammal, fortfarande levande granstubbe # Picea abies</t>
-        </is>
-      </c>
-      <c r="AQ37" t="inlineStr">
-        <is>
-          <t>Alec Bailey</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4903,6 +4808,1871 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132574506</v>
+      </c>
+      <c r="B38" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>V om Lilla Bårsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>591831</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6668470</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>132575020</v>
+      </c>
+      <c r="B39" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lindsberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>591588</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6668491</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132572411</v>
+      </c>
+      <c r="B40" t="n">
+        <v>8270</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>106456</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Granvivel</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pissodes harcyniae</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Herbst, 1795)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>N. om Rudtjärnssjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>591584</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6668502</v>
+      </c>
+      <c r="S40" t="n">
+        <v>20</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Nilsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Nilsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>132574711</v>
+      </c>
+      <c r="B41" t="n">
+        <v>8270</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>106456</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Granvivel</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Pissodes harcyniae</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Herbst, 1795)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>V om Lilla Bårsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>591756</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6668460</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>132574961</v>
+      </c>
+      <c r="B42" t="n">
+        <v>106894</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lindsberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>591583</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6668503</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>40 cm i diameter</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132583662</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lindsberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>591737</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6668436</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Max Karlsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Max Karlsson, Alec Bailey, Malte Lindberg, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132574026</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>V om Lilla Bårsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>591977</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6668522</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>132572429</v>
+      </c>
+      <c r="B45" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>N. om Rudtjärnssjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>591536</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6668450</v>
+      </c>
+      <c r="S45" t="n">
+        <v>9</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Nilsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Nilsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>132574919</v>
+      </c>
+      <c r="B46" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>V om Lilla Bårsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>591599</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6668511</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>132574652</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>V om Lilla Bårsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>591782</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6668502</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Kvarsittande död kvist  # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>132619068</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78381</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6000248</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Mörk kådsvartspik</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis montana</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lindsberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>591762</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6668479</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>K-, sp ~ 4x7</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Barrnaturskog med fuktstråk</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Kåda på en gammal, fortfarande levande granstubbe # Picea abies</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>132619243</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78381</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6000248</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mörk kådsvartspik</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis montana</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>V om Lilla Bårsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>591769</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6668486</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Barrnaturskog med fuktstråk</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Kåda på en gammal, fortfarande levande granstubbe # Picea abies</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Malte Lindberg, Emilia Blixt, Erik Christiansson, Nora Toftgård Shahnavaz, Joel Nilsson, Valdemar Eklund, Valdemar Fredén Zander, Elias Yngvesson, Janka Réthi, Viktor Olofsson, Karla Alfaro Gripe</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>132623089</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78381</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6000248</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Mörk kådsvartspik</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis montana</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lindesbergs , Vstm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>592345</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6668516</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>Ca 15cm i diameter Stubbe med stelnad kåda längs kanten</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies # Ca 15cm i diameter Stubbe med stelnad kåda längs kanten</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Elias Yngvesson, Joel Nilsson, Alec Bailey, Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>132623113</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78381</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6000248</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Mörk kådsvartspik</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis montana</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lindesberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>592243</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6668570</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>7 cm i diameter stubbe med stelnad kåda runt kanten</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies # 7 cm i diameter stubbe med stelnad kåda runt kanten</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Elias Yngvesson, Joel Nilsson, Alec Bailey, Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>132623126</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78381</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6000248</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mörk kådsvartspik</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis montana</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lindesberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>592161</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6668543</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Elias Yngvesson, Joel Nilsson, Alec Bailey, Nora Toftgård Shahnavaz, Malte Lindberg, Max Karlsson, Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13033-2026 artfynd.xlsx
+++ b/artfynd/A 13033-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132572425</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132556382</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132571742</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,6 +1145,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132583652</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132572426</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132561918</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1439,6 +1474,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132583654</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1536,6 +1576,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132556404</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1633,6 +1678,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132567957</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1740,6 +1790,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132572417</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1871,6 +1926,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132574498</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1968,6 +2028,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132558343</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2100,6 +2165,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132572340</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2197,6 +2267,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132554290</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2323,6 +2398,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132574870</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2433,6 +2513,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132583655</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2530,6 +2615,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132567684</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2637,6 +2727,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132572413</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2768,6 +2863,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132572405</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2870,6 +2970,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132566670</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2990,6 +3095,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132572416</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3110,6 +3220,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132572418</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3230,6 +3345,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132572419</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3347,6 +3467,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132572412</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3464,6 +3589,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132572421</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3581,6 +3711,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132572427</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3698,6 +3833,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132572428</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3814,6 +3954,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132583611</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3931,6 +4076,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132572415</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4048,6 +4198,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132572420</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4181,6 +4336,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132574099</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4314,6 +4474,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132574583</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4431,6 +4596,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132572424</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4542,6 +4712,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132574392</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4670,6 +4845,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132574990</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4808,6 +4988,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132575149</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4941,6 +5126,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132574506</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5074,6 +5264,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132575020</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5191,6 +5386,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132572411</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5324,6 +5524,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132574711</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5439,6 +5644,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132574961</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5550,6 +5760,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132583662</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5662,6 +5877,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132574026</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5769,6 +5989,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132572429</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5881,6 +6106,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132574919</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6007,6 +6237,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132574652</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6147,6 +6382,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132619068</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6287,6 +6527,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132619243</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6420,6 +6665,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132623089</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6549,6 +6799,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132623113</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6673,8 +6928,66 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132623126</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>